--- a/verify/MathML4.0問題回復評分表.xlsx
+++ b/verify/MathML4.0問題回復評分表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NCU\SpacialProject\workspace\w3c_rag_chrome_extension\verify\question\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NCU\SpacialProject\workspace\w3c_rag_chrome_extension\verify\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF4C1B3-E4C9-461A-B608-19B85DB9FB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E00B1AD-4698-4EBD-9227-0CCF57E82809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="中文" sheetId="1" r:id="rId1"/>
@@ -4969,9 +4969,11 @@
   <cols>
     <col min="2" max="2" width="66.28515625" customWidth="1"/>
     <col min="3" max="3" width="49.85546875" customWidth="1"/>
-    <col min="4" max="4" width="121.7109375" customWidth="1"/>
-    <col min="5" max="6" width="32.5703125" customWidth="1"/>
-    <col min="7" max="8" width="35.140625" customWidth="1"/>
+    <col min="4" max="4" width="64.7109375" customWidth="1"/>
+    <col min="5" max="5" width="53" customWidth="1"/>
+    <col min="6" max="6" width="48.7109375" customWidth="1"/>
+    <col min="7" max="7" width="39.42578125" customWidth="1"/>
+    <col min="8" max="8" width="50.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -5387,7 +5389,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="300">
+    <row r="17" spans="1:8" ht="299.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -5413,7 +5415,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="409.5">
+    <row r="18" spans="1:8" ht="315">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -5530,10 +5532,10 @@
   <cols>
     <col min="2" max="2" width="169.28515625" customWidth="1"/>
     <col min="3" max="3" width="43.28515625" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="36.7109375" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" customWidth="1"/>
-    <col min="7" max="7" width="24.85546875" customWidth="1"/>
+    <col min="4" max="4" width="39.85546875" customWidth="1"/>
+    <col min="5" max="5" width="53.85546875" customWidth="1"/>
+    <col min="6" max="6" width="43.140625" customWidth="1"/>
+    <col min="7" max="7" width="47.7109375" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
